--- a/Bao cao/TPB/TPB_Model_2026_07_04.xlsx
+++ b/Bao cao/TPB/TPB_Model_2026_07_04.xlsx
@@ -41,7 +41,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +90,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -179,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +208,7 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -211,11 +218,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,9 +233,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -11679,30 +11686,30 @@
           <t>NIM (%)</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>0.0367</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>0.0398</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>0.0393</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>0.0352</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>0.0304</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="17">
         <f>'02_Assumptions'!G6</f>
         <v/>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="17">
         <f>'02_Assumptions'!H6</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="17">
         <f>'02_Assumptions'!I6</f>
         <v/>
       </c>
@@ -11752,30 +11759,30 @@
           <t>ROE (%)</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>0.1858</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>0.215</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>0.1374</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>0.1726</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>0.177</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="17">
         <f>'04_PnL'!G5/AVERAGE('05_Balance_Sheet'!F10,'05_Balance_Sheet'!G10)</f>
         <v/>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="17">
         <f>'04_PnL'!H5/AVERAGE('05_Balance_Sheet'!G10,'05_Balance_Sheet'!H10)</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="17">
         <f>'04_PnL'!I5/AVERAGE('05_Balance_Sheet'!H10,'05_Balance_Sheet'!I10)</f>
         <v/>
       </c>
@@ -11786,30 +11793,30 @@
           <t>ROA (%)</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>0.0165</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>0.0191</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>0.0125</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>0.0145</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>0.0146</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="17">
         <f>'04_PnL'!G5/AVERAGE('05_Balance_Sheet'!F2,'05_Balance_Sheet'!G2)</f>
         <v/>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="17">
         <f>'04_PnL'!H5/AVERAGE('05_Balance_Sheet'!G2,'05_Balance_Sheet'!H2)</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="17">
         <f>'04_PnL'!I5/AVERAGE('05_Balance_Sheet'!H2,'05_Balance_Sheet'!I2)</f>
         <v/>
       </c>
@@ -11848,7 +11855,7 @@
         <f>'05_Balance_Sheet'!H11/'05_Balance_Sheet'!H12</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="17">
         <f>'05_Balance_Sheet'!I11/'05_Balance_Sheet'!I12</f>
         <v/>
       </c>
@@ -11961,19 +11968,19 @@
           <t>YOEA — Lợi suất TSSL (%)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0.0643</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>0.0762</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.0902</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>0.0708</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>0.0698</v>
       </c>
       <c r="G10" s="14" t="n"/>
@@ -11986,19 +11993,19 @@
           <t>COF — Chi phí vốn (%)</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>0.0428</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>0.0534</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.0721</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.051</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>0.0563</v>
       </c>
       <c r="G11" s="14" t="n"/>
@@ -12066,7 +12073,7 @@
           <t>BV/share hiện tại (VND)</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>'05_Balance_Sheet'!F10*1000000000/'02_Assumptions'!$F$3</f>
         <v/>
       </c>
@@ -12077,7 +12084,7 @@
           <t>PV của RI 3 năm (VND)</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>SUM(B31:D31)</f>
         <v/>
       </c>
@@ -12088,7 +12095,7 @@
           <t>PV của Continuing Value (VND)</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>(D29*(1+B3)/(B2-B3))*D30</f>
         <v/>
       </c>
@@ -12117,7 +12124,7 @@
           <t>P/B hiện tại (x)</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>'02_Assumptions'!B2/B6</f>
         <v/>
       </c>
@@ -12128,11 +12135,11 @@
           <t>P/B hấp dẫn (x) — MUA</t>
         </is>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="22">
         <f t="array" ref="B13">MEDIAN(SMALL('13_PE_PB_History'!C2:C32, ROW(INDIRECT("1:"&amp;CEILING(COUNT('13_PE_PB_History'!C2:C32)/2,1)))))</f>
         <v/>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Median P/B nửa dưới (vùng mua hấp dẫn)</t>
         </is>
@@ -12144,11 +12151,11 @@
           <t>P/B median all-time (x) — FAIR VALUE</t>
         </is>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="21">
         <f>MEDIAN('13_PE_PB_History'!C2:C32)</f>
         <v/>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Median PB toàn bộ lịch sử</t>
         </is>
@@ -12160,11 +12167,11 @@
           <t>P/B Over (x) — BÁN / CHỐT LỜI</t>
         </is>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="25">
         <f t="array" ref="B15">MEDIAN(LARGE('13_PE_PB_History'!C2:C32, ROW(INDIRECT("1:"&amp;CEILING(COUNT('13_PE_PB_History'!C2:C32)/2,1)))))</f>
         <v/>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Median P/B nửa trên (vùng chốt lời)</t>
         </is>
@@ -12176,7 +12183,7 @@
           <t>BV/share tương lai (2026F)</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>B6+B26</f>
         <v/>
       </c>
@@ -12223,7 +12230,7 @@
           <t>Giá hiện tại (VND)</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>'02_Assumptions'!B2</f>
         <v/>
       </c>
@@ -12252,15 +12259,15 @@
           <t>EPS (VND)</t>
         </is>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <f>'04_PnL'!G6</f>
         <v/>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>'04_PnL'!H6</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>'04_PnL'!I6</f>
         <v/>
       </c>
@@ -12271,15 +12278,15 @@
           <t>BVPS đầu kỳ (VND)</t>
         </is>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <f>B6</f>
         <v/>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <f>B27+B26</f>
         <v/>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>C27+C26</f>
         <v/>
       </c>
@@ -12290,15 +12297,15 @@
           <t>Capital Charge (VND)</t>
         </is>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <f>B27*'07_Valuation'!$B$2</f>
         <v/>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>C27*'07_Valuation'!$B$2</f>
         <v/>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>D27*'07_Valuation'!$B$2</f>
         <v/>
       </c>
@@ -12309,15 +12316,15 @@
           <t>Residual Income (VND)</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <f>B26-B28</f>
         <v/>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="20">
         <f>C26-C28</f>
         <v/>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <f>D26-D28</f>
         <v/>
       </c>
@@ -12328,15 +12335,15 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <f>1/(1+'07_Valuation'!$B$2)^1</f>
         <v/>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="27">
         <f>1/(1+'07_Valuation'!$B$2)^2</f>
         <v/>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="27">
         <f>1/(1+'07_Valuation'!$B$2)^3</f>
         <v/>
       </c>
@@ -12347,15 +12354,15 @@
           <t>PV of RI</t>
         </is>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="20">
         <f>B29*B30</f>
         <v/>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="20">
         <f>C29*C30</f>
         <v/>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="20">
         <f>D29*D30</f>
         <v/>
       </c>
@@ -12387,120 +12394,120 @@
           <t>COE \ g</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="28" t="n">
         <v>0.01</v>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="D2" s="27" t="n">
+      <c r="D2" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="E2" s="27" t="n">
+      <c r="E2" s="28" t="n">
         <v>0.04</v>
       </c>
-      <c r="F2" s="27" t="n">
+      <c r="F2" s="28" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="n">
+      <c r="A3" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="B3" s="19" t="n">
-        <v>34435.0945382376</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>37119.50918819172</v>
-      </c>
-      <c r="D3" s="19" t="n">
-        <v>40877.68969812748</v>
-      </c>
-      <c r="E3" s="19" t="n">
-        <v>46514.96046303112</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>55910.41173787051</v>
+      <c r="B3" s="20" t="n">
+        <v>33975.09571142335</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>36590.61661610764</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>40252.34588266566</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>45744.93978250267</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>54899.26294889771</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="B4" s="19" t="n">
-        <v>30354.57699398342</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>31864.06106656919</v>
-      </c>
-      <c r="D4" s="19" t="n">
-        <v>33804.82630275089</v>
-      </c>
-      <c r="E4" s="19" t="n">
-        <v>36392.51328432649</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>40015.27505853233</v>
+      <c r="B4" s="20" t="n">
+        <v>29999.37520092135</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>31470.11935261325</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>33361.07611907426</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>35882.35180768893</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>39412.13777174948</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="29" t="n">
         <v>0.12</v>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>27761.77585418046</v>
-      </c>
-      <c r="C5" s="29" t="n">
-        <v>28714.83021123397</v>
-      </c>
-      <c r="D5" s="29" t="n">
-        <v>29879.67442541049</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>31335.72969313114</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>33207.80075162911</v>
+      <c r="B5" s="20" t="n">
+        <v>27473.18609056083</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>28401.78093123365</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>29536.73018094487</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>30955.41674308389</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>32779.44232297693</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>25969.85892753128</v>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>26618.51143404055</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>27385.10075991513</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>28305.00795096463</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>29429.33896224735</v>
+      <c r="B6" s="20" t="n">
+        <v>25727.32354239369</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>26359.32880681134</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>27106.24411930491</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>28002.5424942972</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>29098.01828595445</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
+      <c r="A7" s="29" t="n">
         <v>0.16</v>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>24658.3173171619</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>25123.70097466881</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>25660.68211794601</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>26287.16011843608</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>27027.54320992434</v>
+      <c r="B7" s="20" t="n">
+        <v>24449.50454378069</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>24902.94443427173</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>25426.14430791525</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>26036.54416049935</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>26757.92580446238</v>
       </c>
     </row>
   </sheetData>
@@ -12890,35 +12897,35 @@
           <t>Thu nhập lãi thuần (NII)</t>
         </is>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="19">
         <f>'04_PnL'!B2</f>
         <v/>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="19">
         <f>'04_PnL'!C2</f>
         <v/>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="19">
         <f>'04_PnL'!D2</f>
         <v/>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <f>'04_PnL'!E2</f>
         <v/>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="19">
         <f>'04_PnL'!F2</f>
         <v/>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="19">
         <f>'04_PnL'!G2</f>
         <v/>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="19">
         <f>'04_PnL'!H2</f>
         <v/>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="19">
         <f>'04_PnL'!I2</f>
         <v/>
       </c>
@@ -12929,35 +12936,35 @@
           <t>Tổng thu nhập HĐ (TOI)</t>
         </is>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="19">
         <f>'04_PnL'!B3</f>
         <v/>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="19">
         <f>'04_PnL'!C3</f>
         <v/>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="19">
         <f>'04_PnL'!D3</f>
         <v/>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="19">
         <f>'04_PnL'!E3</f>
         <v/>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="19">
         <f>'04_PnL'!F3</f>
         <v/>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="19">
         <f>'04_PnL'!G3</f>
         <v/>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="19">
         <f>'04_PnL'!H3</f>
         <v/>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="19">
         <f>'04_PnL'!I3</f>
         <v/>
       </c>
@@ -12968,35 +12975,35 @@
           <t>LN trước dự phòng (PPOP)</t>
         </is>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>'04_PnL'!B4</f>
         <v/>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <f>'04_PnL'!C4</f>
         <v/>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="19">
         <f>'04_PnL'!D4</f>
         <v/>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="19">
         <f>'04_PnL'!E4</f>
         <v/>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="19">
         <f>'04_PnL'!F4</f>
         <v/>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="19">
         <f>'04_PnL'!G4</f>
         <v/>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="19">
         <f>'04_PnL'!H4</f>
         <v/>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="19">
         <f>'04_PnL'!I4</f>
         <v/>
       </c>
@@ -13007,35 +13014,35 @@
           <t>LNST (NPAT)</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'04_PnL'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'04_PnL'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'04_PnL'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'04_PnL'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'04_PnL'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'04_PnL'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'04_PnL'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="19">
         <f>'04_PnL'!I5</f>
         <v/>
       </c>
@@ -13046,35 +13053,35 @@
           <t>EPS (VND)</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>'04_PnL'!B6</f>
         <v/>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>'04_PnL'!C6</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>'04_PnL'!D6</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>'04_PnL'!E6</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <f>'04_PnL'!F6</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>'04_PnL'!G6</f>
         <v/>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <f>'04_PnL'!H6</f>
         <v/>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <f>'04_PnL'!I6</f>
         <v/>
       </c>
@@ -13085,35 +13092,35 @@
           <t>Tổng tài sản</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>'05_Balance_Sheet'!B2</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>'05_Balance_Sheet'!C2</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>'05_Balance_Sheet'!D2</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>'05_Balance_Sheet'!E2</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="19">
         <f>'05_Balance_Sheet'!F2</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="19">
         <f>'05_Balance_Sheet'!G2</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="19">
         <f>'05_Balance_Sheet'!H2</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="19">
         <f>'05_Balance_Sheet'!I2</f>
         <v/>
       </c>
@@ -13124,35 +13131,35 @@
           <t>Cho vay khách hàng (Gross)</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>'05_Balance_Sheet'!B3</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>'05_Balance_Sheet'!C3</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>'05_Balance_Sheet'!D3</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>'05_Balance_Sheet'!E3</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>'05_Balance_Sheet'!F3</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="19">
         <f>'05_Balance_Sheet'!G3</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="19">
         <f>'05_Balance_Sheet'!H3</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="19">
         <f>'05_Balance_Sheet'!I3</f>
         <v/>
       </c>
@@ -13163,35 +13170,35 @@
           <t>Trái phiếu doanh nghiệp</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>'05_Balance_Sheet'!B4</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>'05_Balance_Sheet'!C4</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>'05_Balance_Sheet'!D4</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>'05_Balance_Sheet'!E4</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>'05_Balance_Sheet'!F4</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>'05_Balance_Sheet'!G4</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>'05_Balance_Sheet'!H4</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="19">
         <f>'05_Balance_Sheet'!I4</f>
         <v/>
       </c>
@@ -13202,35 +13209,35 @@
           <t>Tiền gửi khách hàng</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>'05_Balance_Sheet'!B5</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>'05_Balance_Sheet'!C5</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>'05_Balance_Sheet'!D5</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>'05_Balance_Sheet'!E5</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>'05_Balance_Sheet'!F5</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>'05_Balance_Sheet'!G5</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>'05_Balance_Sheet'!H5</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="19">
         <f>'05_Balance_Sheet'!I5</f>
         <v/>
       </c>
@@ -13241,35 +13248,35 @@
           <t>Giấy tờ có giá (Bonds)</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>'05_Balance_Sheet'!B6</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>'05_Balance_Sheet'!C6</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>'05_Balance_Sheet'!D6</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>'05_Balance_Sheet'!E6</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>'05_Balance_Sheet'!F6</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>'05_Balance_Sheet'!G6</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>'05_Balance_Sheet'!H6</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="19">
         <f>'05_Balance_Sheet'!I6</f>
         <v/>
       </c>
@@ -13280,35 +13287,35 @@
           <t>Tiền gửi Kho bạc NN</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <f>'05_Balance_Sheet'!B7</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>'05_Balance_Sheet'!C7</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>'05_Balance_Sheet'!D7</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>'05_Balance_Sheet'!E7</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>'05_Balance_Sheet'!F7</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>'05_Balance_Sheet'!G7</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>'05_Balance_Sheet'!H7</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="19">
         <f>'05_Balance_Sheet'!I7</f>
         <v/>
       </c>
@@ -13319,35 +13326,35 @@
           <t>Tiền gửi ký quỹ (trừ đi)</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <f>'05_Balance_Sheet'!B8</f>
         <v/>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <f>'05_Balance_Sheet'!C8</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>'05_Balance_Sheet'!D8</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>'05_Balance_Sheet'!E8</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>'05_Balance_Sheet'!F8</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>'05_Balance_Sheet'!G8</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="19">
         <f>'05_Balance_Sheet'!H8</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="19">
         <f>'05_Balance_Sheet'!I8</f>
         <v/>
       </c>
@@ -13358,35 +13365,35 @@
           <t>Vốn chuyên dùng (trừ đi)</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <f>'05_Balance_Sheet'!B9</f>
         <v/>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <f>'05_Balance_Sheet'!C9</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="19">
         <f>'05_Balance_Sheet'!D9</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>'05_Balance_Sheet'!E9</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <f>'05_Balance_Sheet'!F9</f>
         <v/>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="19">
         <f>'05_Balance_Sheet'!G9</f>
         <v/>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="19">
         <f>'05_Balance_Sheet'!H9</f>
         <v/>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="19">
         <f>'05_Balance_Sheet'!I9</f>
         <v/>
       </c>
@@ -13397,35 +13404,35 @@
           <t>Vốn chủ sở hữu (VCSH)</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <f>'05_Balance_Sheet'!B10</f>
         <v/>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <f>'05_Balance_Sheet'!C10</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="19">
         <f>'05_Balance_Sheet'!D10</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>'05_Balance_Sheet'!E10</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <f>'05_Balance_Sheet'!F10</f>
         <v/>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="19">
         <f>'05_Balance_Sheet'!G10</f>
         <v/>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="19">
         <f>'05_Balance_Sheet'!H10</f>
         <v/>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="19">
         <f>'05_Balance_Sheet'!I10</f>
         <v/>
       </c>
@@ -13484,10 +13491,10 @@
           <t>Q3/18</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>11.1112176348</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>1.6962244564</v>
       </c>
       <c r="D2" s="14" t="n"/>
@@ -13499,10 +13506,10 @@
           <t>Q4/18</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>10.7581213311</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>1.7341574885</v>
       </c>
       <c r="D3" s="14" t="n"/>
@@ -13514,10 +13521,10 @@
           <t>Q1/19</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>10.4864961407</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>1.7697443122</v>
       </c>
       <c r="D4" s="14" t="n"/>
@@ -13529,10 +13536,10 @@
           <t>Q2/19</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>9.453410806000001</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>1.6615287124</v>
       </c>
       <c r="D5" s="14" t="n"/>
@@ -13544,10 +13551,10 @@
           <t>Q3/19</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>8.5476768085</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>1.6631167951</v>
       </c>
       <c r="D6" s="14" t="n"/>
@@ -13559,10 +13566,10 @@
           <t>Q4/19</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>7.5211060378</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>1.4922334255</v>
       </c>
       <c r="D7" s="14" t="n"/>
@@ -13574,10 +13581,10 @@
           <t>Q1/20</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>5.0667042338</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>1.1429182043</v>
       </c>
       <c r="D8" s="14" t="n"/>
@@ -13589,10 +13596,10 @@
           <t>Q2/20</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>5.7002160336</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>1.28704704</v>
       </c>
       <c r="D9" s="14" t="n"/>
@@ -13604,10 +13611,10 @@
           <t>Q3/20</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>6.2364756386</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>1.4474192213</v>
       </c>
       <c r="D10" s="14" t="n"/>
@@ -13619,10 +13626,10 @@
           <t>Q4/20</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>7.8977016108</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>1.8644294968</v>
       </c>
       <c r="D11" s="14" t="n"/>
@@ -13634,10 +13641,10 @@
           <t>Q1/21</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>8.4263664777</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>1.7004908974</v>
       </c>
       <c r="D12" s="14" t="n"/>
@@ -13649,10 +13656,10 @@
           <t>Q2/21</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>9.3528859821</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>2.092616043</v>
       </c>
       <c r="D13" s="14" t="n"/>
@@ -13664,10 +13671,10 @@
           <t>Q3/21</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>12.3724572142</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>2.4851555267</v>
       </c>
       <c r="D14" s="14" t="n"/>
@@ -13679,10 +13686,10 @@
           <t>Q4/21</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <v>11.6476620675</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>2.2733831763</v>
       </c>
       <c r="D15" s="14" t="n"/>
@@ -13694,10 +13701,10 @@
           <t>Q1/22</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <v>8.227537460600001</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1.5395562861</v>
       </c>
       <c r="D16" s="14" t="n"/>
@@ -13709,10 +13716,10 @@
           <t>Q2/22</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>5.932968923</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>1.1232780137</v>
       </c>
       <c r="D17" s="14" t="n"/>
@@ -13724,10 +13731,10 @@
           <t>Q3/22</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <v>5.8833610578</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <v>1.1564767588</v>
       </c>
       <c r="D18" s="14" t="n"/>
@@ -13739,10 +13746,10 @@
           <t>Q4/22</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <v>5.8948106007</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="18" t="n">
         <v>1.1382694343</v>
       </c>
       <c r="D19" s="14" t="n"/>
@@ -13754,10 +13761,10 @@
           <t>Q1/23</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <v>6.2941922868</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="18" t="n">
         <v>1.1870752659</v>
       </c>
       <c r="D20" s="14" t="n"/>
@@ -13769,10 +13776,10 @@
           <t>Q2/23</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="18" t="n">
         <v>6.4041260533</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="18" t="n">
         <v>1.2221066515</v>
       </c>
       <c r="D21" s="14" t="n"/>
@@ -13784,10 +13791,10 @@
           <t>Q3/23</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="18" t="n">
         <v>7.4715236957</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="18" t="n">
         <v>1.2611292264</v>
       </c>
       <c r="D22" s="14" t="n"/>
@@ -13799,10 +13806,10 @@
           <t>Q4/23</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="18" t="n">
         <v>9.261968377600001</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="18" t="n">
         <v>1.2573887253</v>
       </c>
       <c r="D23" s="14" t="n"/>
@@ -13814,10 +13821,10 @@
           <t>Q1/24</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="18" t="n">
         <v>8.793273769200001</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="18" t="n">
         <v>1.1558724836</v>
       </c>
       <c r="D24" s="14" t="n"/>
@@ -13829,10 +13836,10 @@
           <t>Q2/24</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="18" t="n">
         <v>9.7550014762</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="18" t="n">
         <v>1.2946798123</v>
       </c>
       <c r="D25" s="14" t="n"/>
@@ -13844,10 +13851,10 @@
           <t>Q3/24</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="18" t="n">
         <v>8.6688081709</v>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="18" t="n">
         <v>1.1568704257</v>
       </c>
       <c r="D26" s="14" t="n"/>
@@ -13859,10 +13866,10 @@
           <t>Q4/24</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="18" t="n">
         <v>5.5886841516</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <v>0.8995240327</v>
       </c>
       <c r="D27" s="14" t="n"/>
@@ -13874,10 +13881,10 @@
           <t>Q1/25</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="18" t="n">
         <v>6.274213445</v>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="18" t="n">
         <v>0.9968005599999999</v>
       </c>
       <c r="D28" s="14" t="n"/>
@@ -13889,10 +13896,10 @@
           <t>Q2/25</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="18" t="n">
         <v>7.9497194512</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="18" t="n">
         <v>1.3268587776</v>
       </c>
       <c r="D29" s="14" t="n"/>
@@ -13904,10 +13911,10 @@
           <t>Q3/25</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="18" t="n">
         <v>7.4468197397</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="18" t="n">
         <v>1.2138536221</v>
       </c>
       <c r="D30" s="14" t="n"/>
@@ -13919,10 +13926,10 @@
           <t>Q4/25</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="18" t="n">
         <v>6.1662026616</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="18" t="n">
         <v>1.0753642028</v>
       </c>
       <c r="D31" s="14" t="n"/>
@@ -13934,29 +13941,29 @@
           <t>Q1/26</t>
         </is>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="18" t="n">
         <v>6.2403008183</v>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C32" s="18" t="n">
         <v>1.0350579991</v>
       </c>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>MEDIAN ALL-TIME</t>
         </is>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <v>7.8977016108</v>
       </c>
-      <c r="C34" s="32" t="n">
+      <c r="C34" s="33" t="n">
         <v>1.28704704</v>
       </c>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
+      <c r="D34" s="34" t="n"/>
+      <c r="E34" s="34" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14007,409 +14014,409 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>Q4/21</t>
         </is>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="35">
         <f>'05_Balance_Sheet_Quarterly'!B5+'05_Balance_Sheet_Quarterly'!B9</f>
         <v/>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="35">
         <f>'05_Balance_Sheet_Quarterly'!B7+'05_Balance_Sheet_Quarterly'!B10+'05_Balance_Sheet_Quarterly'!B11*0.0-'05_Balance_Sheet_Quarterly'!B12-'05_Balance_Sheet_Quarterly'!B13</f>
         <v/>
       </c>
-      <c r="D2" s="33" t="n"/>
-      <c r="E2" s="33" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>Q1/22</t>
         </is>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="35">
         <f>'05_Balance_Sheet_Quarterly'!C5+'05_Balance_Sheet_Quarterly'!C9</f>
         <v/>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="35">
         <f>'05_Balance_Sheet_Quarterly'!C7+'05_Balance_Sheet_Quarterly'!C10+'05_Balance_Sheet_Quarterly'!C11*0.0-'05_Balance_Sheet_Quarterly'!C12-'05_Balance_Sheet_Quarterly'!C13</f>
         <v/>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="36">
         <f>(B3-B2)/B2</f>
         <v/>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="36">
         <f>(C3-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Q2/22</t>
         </is>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="35">
         <f>'05_Balance_Sheet_Quarterly'!D5+'05_Balance_Sheet_Quarterly'!D9</f>
         <v/>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="35">
         <f>'05_Balance_Sheet_Quarterly'!D7+'05_Balance_Sheet_Quarterly'!D10+'05_Balance_Sheet_Quarterly'!D11*0.0-'05_Balance_Sheet_Quarterly'!D12-'05_Balance_Sheet_Quarterly'!D13</f>
         <v/>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <f>(B4-B2)/B2</f>
         <v/>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <f>(C4-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Q3/22</t>
         </is>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="35">
         <f>'05_Balance_Sheet_Quarterly'!E5+'05_Balance_Sheet_Quarterly'!E9</f>
         <v/>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <f>'05_Balance_Sheet_Quarterly'!E7+'05_Balance_Sheet_Quarterly'!E10+'05_Balance_Sheet_Quarterly'!E11*0.0-'05_Balance_Sheet_Quarterly'!E12-'05_Balance_Sheet_Quarterly'!E13</f>
         <v/>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="36">
         <f>(B5-B2)/B2</f>
         <v/>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="36">
         <f>(C5-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Q4/22</t>
         </is>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="35">
         <f>'05_Balance_Sheet_Quarterly'!F5+'05_Balance_Sheet_Quarterly'!F9</f>
         <v/>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="35">
         <f>'05_Balance_Sheet_Quarterly'!F7+'05_Balance_Sheet_Quarterly'!F10+'05_Balance_Sheet_Quarterly'!F11*0.0-'05_Balance_Sheet_Quarterly'!F12-'05_Balance_Sheet_Quarterly'!F13</f>
         <v/>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="36">
         <f>(B6-B2)/B2</f>
         <v/>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="36">
         <f>(C6-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Q1/23</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="35">
         <f>'05_Balance_Sheet_Quarterly'!G5+'05_Balance_Sheet_Quarterly'!G9</f>
         <v/>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="35">
         <f>'05_Balance_Sheet_Quarterly'!G7+'05_Balance_Sheet_Quarterly'!G10+'05_Balance_Sheet_Quarterly'!G11*0.5-'05_Balance_Sheet_Quarterly'!G12-'05_Balance_Sheet_Quarterly'!G13</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="36">
         <f>(B7-B6)/B6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="36">
         <f>(C7-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Q2/23</t>
         </is>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="35">
         <f>'05_Balance_Sheet_Quarterly'!H5+'05_Balance_Sheet_Quarterly'!H9</f>
         <v/>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <f>'05_Balance_Sheet_Quarterly'!H7+'05_Balance_Sheet_Quarterly'!H10+'05_Balance_Sheet_Quarterly'!H11*0.5-'05_Balance_Sheet_Quarterly'!H12-'05_Balance_Sheet_Quarterly'!H13</f>
         <v/>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="36">
         <f>(B8-B6)/B6</f>
         <v/>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="36">
         <f>(C8-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Q3/23</t>
         </is>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>'05_Balance_Sheet_Quarterly'!I5+'05_Balance_Sheet_Quarterly'!I9</f>
         <v/>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <f>'05_Balance_Sheet_Quarterly'!I7+'05_Balance_Sheet_Quarterly'!I10+'05_Balance_Sheet_Quarterly'!I11*0.5-'05_Balance_Sheet_Quarterly'!I12-'05_Balance_Sheet_Quarterly'!I13</f>
         <v/>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <f>(B9-B6)/B6</f>
         <v/>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="36">
         <f>(C9-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Q4/23</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>'05_Balance_Sheet_Quarterly'!J5+'05_Balance_Sheet_Quarterly'!J9</f>
         <v/>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>'05_Balance_Sheet_Quarterly'!J7+'05_Balance_Sheet_Quarterly'!J10+'05_Balance_Sheet_Quarterly'!J11*0.5-'05_Balance_Sheet_Quarterly'!J12-'05_Balance_Sheet_Quarterly'!J13</f>
         <v/>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="36">
         <f>(B10-B6)/B6</f>
         <v/>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="36">
         <f>(C10-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Q1/24</t>
         </is>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>'05_Balance_Sheet_Quarterly'!K5+'05_Balance_Sheet_Quarterly'!K9</f>
         <v/>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <f>'05_Balance_Sheet_Quarterly'!K7+'05_Balance_Sheet_Quarterly'!K10+'05_Balance_Sheet_Quarterly'!K11*0.4-'05_Balance_Sheet_Quarterly'!K12-'05_Balance_Sheet_Quarterly'!K13</f>
         <v/>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <f>(B11-B10)/B10</f>
         <v/>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <f>(C11-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Q2/24</t>
         </is>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="35">
         <f>'05_Balance_Sheet_Quarterly'!L5+'05_Balance_Sheet_Quarterly'!L9</f>
         <v/>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="35">
         <f>'05_Balance_Sheet_Quarterly'!L7+'05_Balance_Sheet_Quarterly'!L10+'05_Balance_Sheet_Quarterly'!L11*0.4-'05_Balance_Sheet_Quarterly'!L12-'05_Balance_Sheet_Quarterly'!L13</f>
         <v/>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="36">
         <f>(B12-B10)/B10</f>
         <v/>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="36">
         <f>(C12-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Q3/24</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="35">
         <f>'05_Balance_Sheet_Quarterly'!M5+'05_Balance_Sheet_Quarterly'!M9</f>
         <v/>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="35">
         <f>'05_Balance_Sheet_Quarterly'!M7+'05_Balance_Sheet_Quarterly'!M10+'05_Balance_Sheet_Quarterly'!M11*0.4-'05_Balance_Sheet_Quarterly'!M12-'05_Balance_Sheet_Quarterly'!M13</f>
         <v/>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="36">
         <f>(B13-B10)/B10</f>
         <v/>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="36">
         <f>(C13-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Q4/24</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>'05_Balance_Sheet_Quarterly'!N5+'05_Balance_Sheet_Quarterly'!N9</f>
         <v/>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>'05_Balance_Sheet_Quarterly'!N7+'05_Balance_Sheet_Quarterly'!N10+'05_Balance_Sheet_Quarterly'!N11*0.4-'05_Balance_Sheet_Quarterly'!N12-'05_Balance_Sheet_Quarterly'!N13</f>
         <v/>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="36">
         <f>(B14-B10)/B10</f>
         <v/>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>(C14-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Q1/25</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>'05_Balance_Sheet_Quarterly'!O5+'05_Balance_Sheet_Quarterly'!O9</f>
         <v/>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>'05_Balance_Sheet_Quarterly'!O7+'05_Balance_Sheet_Quarterly'!O10+'05_Balance_Sheet_Quarterly'!O11*0.2-'05_Balance_Sheet_Quarterly'!O12-'05_Balance_Sheet_Quarterly'!O13</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>(B15-B14)/B14</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>(C15-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Q2/25</t>
         </is>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>'05_Balance_Sheet_Quarterly'!P5+'05_Balance_Sheet_Quarterly'!P9</f>
         <v/>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="35">
         <f>'05_Balance_Sheet_Quarterly'!P7+'05_Balance_Sheet_Quarterly'!P10+'05_Balance_Sheet_Quarterly'!P11*0.2-'05_Balance_Sheet_Quarterly'!P12-'05_Balance_Sheet_Quarterly'!P13</f>
         <v/>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="36">
         <f>(B16-B14)/B14</f>
         <v/>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="36">
         <f>(C16-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Q3/25</t>
         </is>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <f>'05_Balance_Sheet_Quarterly'!Q5+'05_Balance_Sheet_Quarterly'!Q9</f>
         <v/>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="35">
         <f>'05_Balance_Sheet_Quarterly'!Q7+'05_Balance_Sheet_Quarterly'!Q10+'05_Balance_Sheet_Quarterly'!Q11*0.2-'05_Balance_Sheet_Quarterly'!Q12-'05_Balance_Sheet_Quarterly'!Q13</f>
         <v/>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="36">
         <f>(B17-B14)/B14</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="36">
         <f>(C17-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Q4/25</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>'05_Balance_Sheet_Quarterly'!R5+'05_Balance_Sheet_Quarterly'!R9</f>
         <v/>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <f>'05_Balance_Sheet_Quarterly'!R7+'05_Balance_Sheet_Quarterly'!R10+'05_Balance_Sheet_Quarterly'!R11*0.2-'05_Balance_Sheet_Quarterly'!R12-'05_Balance_Sheet_Quarterly'!R13</f>
         <v/>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="36">
         <f>(B18-B14)/B14</f>
         <v/>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="36">
         <f>(C18-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Q1/26</t>
         </is>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="35">
         <f>'05_Balance_Sheet_Quarterly'!S5+'05_Balance_Sheet_Quarterly'!S9</f>
         <v/>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="35">
         <f>'05_Balance_Sheet_Quarterly'!S7+'05_Balance_Sheet_Quarterly'!S10+'05_Balance_Sheet_Quarterly'!S11*0.2-'05_Balance_Sheet_Quarterly'!S12-'05_Balance_Sheet_Quarterly'!S13</f>
         <v/>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="36">
         <f>(B19-B18)/B18</f>
         <v/>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="36">
         <f>(C19-C18)/C18</f>
         <v/>
       </c>
@@ -14586,593 +14593,593 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Trung bình ngành</t>
         </is>
       </c>
-      <c r="B2" s="37" t="n">
+      <c r="B2" s="38" t="n">
         <v>2.385</v>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="38" t="n">
         <v>4.357222222222222</v>
       </c>
-      <c r="D2" s="37" t="n">
+      <c r="D2" s="38" t="n">
         <v>16.84888888888889</v>
       </c>
-      <c r="E2" s="37" t="n">
+      <c r="E2" s="38" t="n">
         <v>15.58666666666667</v>
       </c>
-      <c r="F2" s="37" t="n">
+      <c r="F2" s="38" t="n">
         <v>33.94777777777777</v>
       </c>
-      <c r="G2" s="38" t="n">
+      <c r="G2" s="39" t="n">
         <v>1.454444444444444</v>
       </c>
-      <c r="H2" s="37" t="n">
+      <c r="H2" s="38" t="n">
         <v>3.509444444444445</v>
       </c>
-      <c r="I2" s="36" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>VCB — Vietcombank</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="36" t="n">
         <v>0.0063</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="36" t="n">
         <v>0.0409</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="36" t="n">
         <v>0.3255</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="36" t="n">
         <v>0.1617</v>
       </c>
-      <c r="F3" s="35" t="n">
+      <c r="F3" s="36" t="n">
         <v>0.325</v>
       </c>
-      <c r="G3" s="39" t="n">
+      <c r="G3" s="40" t="n">
         <v>2.21</v>
       </c>
-      <c r="H3" s="35" t="n">
+      <c r="H3" s="36" t="n">
         <v>0.0478</v>
       </c>
-      <c r="I3" s="34" t="n">
+      <c r="I3" s="35" t="n">
         <v>518051.855828</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>BID — BIDV</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="36" t="n">
         <v>0.0178</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="36" t="n">
         <v>0.0263</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="36" t="n">
         <v>0.1949</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="36" t="n">
         <v>0.1443</v>
       </c>
-      <c r="F4" s="35" t="n">
+      <c r="F4" s="36" t="n">
         <v>0.3202</v>
       </c>
-      <c r="G4" s="39" t="n">
+      <c r="G4" s="40" t="n">
         <v>1.61</v>
       </c>
-      <c r="H4" s="35" t="n">
+      <c r="H4" s="36" t="n">
         <v>0.0233</v>
       </c>
-      <c r="I4" s="34" t="n">
+      <c r="I4" s="35" t="n">
         <v>307582.7551225</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>CTG — VietinBank</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="36" t="n">
         <v>0.0103</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="36" t="n">
         <v>0.0389</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="36" t="n">
         <v>0.2408</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="36" t="n">
         <v>0.1899</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="36" t="n">
         <v>0.2494</v>
       </c>
-      <c r="G5" s="39" t="n">
+      <c r="G5" s="40" t="n">
         <v>1.41</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="36" t="n">
         <v>0.0187</v>
       </c>
-      <c r="I5" s="34" t="n">
+      <c r="I5" s="35" t="n">
         <v>265241.15935355</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>TCB — Techcombank</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>0.0111</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="36" t="n">
         <v>0.04849999999999999</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="36" t="n">
         <v>0.3145</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="36" t="n">
         <v>0.1489</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="36" t="n">
         <v>0.2829</v>
       </c>
-      <c r="G6" s="39" t="n">
+      <c r="G6" s="40" t="n">
         <v>1.28</v>
       </c>
-      <c r="H6" s="35" t="n">
+      <c r="H6" s="36" t="n">
         <v>0.03759999999999999</v>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="I6" s="35" t="n">
         <v>238097.6779104</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>MBB — MBBank</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>0.0144</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>0.0539</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="36" t="n">
         <v>0.3227</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="36" t="n">
         <v>0.2058</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="36" t="n">
         <v>0.2494</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="40" t="n">
         <v>1.38</v>
       </c>
-      <c r="H7" s="35" t="n">
+      <c r="H7" s="36" t="n">
         <v>0.0327</v>
       </c>
-      <c r="I7" s="34" t="n">
+      <c r="I7" s="35" t="n">
         <v>206207.9976704</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>ACB — ACB</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="36" t="n">
         <v>0.0098</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="36" t="n">
         <v>0.0399</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="36" t="n">
         <v>0.2123</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="36" t="n">
         <v>0.175</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="36" t="n">
         <v>0.3201</v>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="40" t="n">
         <v>1.33</v>
       </c>
-      <c r="H8" s="35" t="n">
+      <c r="H8" s="36" t="n">
         <v>0.0325</v>
       </c>
-      <c r="I8" s="34" t="n">
+      <c r="I8" s="35" t="n">
         <v>131470.15732605</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>VIB — VIB</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="36" t="n">
         <v>0.0298</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="36" t="n">
         <v>0.0424</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="36" t="n">
         <v>0.1393</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="36" t="n">
         <v>0.1824</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="36" t="n">
         <v>0.3161</v>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="40" t="n">
         <v>1.14</v>
       </c>
-      <c r="H9" s="35" t="n">
+      <c r="H9" s="36" t="n">
         <v>0.0113</v>
       </c>
-      <c r="I9" s="34" t="n">
+      <c r="I9" s="35" t="n">
         <v>55995.8939295</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>HDB — HDBank</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="36" t="n">
         <v>0.0264</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="36" t="n">
         <v>0.0572</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="36" t="n">
         <v>0.1021</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="36" t="n">
         <v>0.2357</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="36" t="n">
         <v>0.2599</v>
       </c>
-      <c r="G10" s="39" t="n">
+      <c r="G10" s="40" t="n">
         <v>1.62</v>
       </c>
-      <c r="H10" s="35" t="n">
+      <c r="H10" s="36" t="n">
         <v>0.1006</v>
       </c>
-      <c r="I10" s="34" t="n">
+      <c r="I10" s="35" t="n">
         <v>134892.19690485</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>STB — Sacombank</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="36" t="n">
         <v>0.06860000000000001</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="36" t="n">
         <v>0.04</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="36" t="n">
         <v>0.1592</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="36" t="n">
         <v>0.1031</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="36" t="n">
         <v>0.4521</v>
       </c>
-      <c r="G11" s="39" t="n">
+      <c r="G11" s="40" t="n">
         <v>2.21</v>
       </c>
-      <c r="H11" s="35" t="n">
+      <c r="H11" s="36" t="n">
         <v>-0.0024</v>
       </c>
-      <c r="I11" s="34" t="n">
+      <c r="I11" s="35" t="n">
         <v>135735.531552</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>VPB — VPBank</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="36" t="n">
         <v>0.0365</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="36" t="n">
         <v>0.0664</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="36" t="n">
         <v>0.1309</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="36" t="n">
         <v>0.1357</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="36" t="n">
         <v>0.2169</v>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G12" s="40" t="n">
         <v>1.18</v>
       </c>
-      <c r="H12" s="35" t="n">
+      <c r="H12" s="36" t="n">
         <v>0.1023</v>
       </c>
-      <c r="I12" s="34" t="n">
+      <c r="I12" s="35" t="n">
         <v>220563.0761078</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>TPB — TPBank</t>
         </is>
       </c>
-      <c r="B13" s="41" t="n">
+      <c r="B13" s="42" t="n">
         <v>0.0219</v>
       </c>
-      <c r="C13" s="41" t="n">
+      <c r="C13" s="42" t="n">
         <v>0.0443</v>
       </c>
-      <c r="D13" s="41" t="n">
+      <c r="D13" s="42" t="n">
         <v>0.1745</v>
       </c>
-      <c r="E13" s="41" t="n">
+      <c r="E13" s="42" t="n">
         <v>0.1401</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="42" t="n">
         <v>0.4585</v>
       </c>
-      <c r="G13" s="42" t="n">
+      <c r="G13" s="43" t="n">
         <v>0.96</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="42" t="n">
         <v>0.0326</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="44" t="n">
         <v>45910.47574815</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>MSB — MSB</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="36" t="n">
         <v>0.027</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="36" t="n">
         <v>0.0604</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="36" t="n">
         <v>0.2551</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="36" t="n">
         <v>0.1377</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="36" t="n">
         <v>0.3451</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="40" t="n">
         <v>1.14</v>
       </c>
-      <c r="H14" s="35" t="n">
+      <c r="H14" s="36" t="n">
         <v>0.0464</v>
       </c>
-      <c r="I14" s="34" t="n">
+      <c r="I14" s="35" t="n">
         <v>49920</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>EIB — Eximbank</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="36" t="n">
         <v>0.031</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="36" t="n">
         <v>0.0295</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="36" t="n">
         <v>0.1337</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="36" t="n">
         <v>0.0407</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="36" t="n">
         <v>0.5698</v>
       </c>
-      <c r="G15" s="39" t="n">
+      <c r="G15" s="40" t="n">
         <v>1.46</v>
       </c>
-      <c r="H15" s="35" t="n">
+      <c r="H15" s="36" t="n">
         <v>0.0289</v>
       </c>
-      <c r="I15" s="34" t="n">
+      <c r="I15" s="35" t="n">
         <v>38465.18053455</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>LPB — LienVietPostBank</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="36" t="n">
         <v>0.0186</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="36" t="n">
         <v>0.039</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="36" t="n">
         <v>0.0649</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="36" t="n">
         <v>0.1843</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="36" t="n">
         <v>0.3014</v>
       </c>
-      <c r="G16" s="39" t="n">
+      <c r="G16" s="40" t="n">
         <v>3.08</v>
       </c>
-      <c r="H16" s="35" t="n">
+      <c r="H16" s="36" t="n">
         <v>0.0284</v>
       </c>
-      <c r="I16" s="34" t="n">
+      <c r="I16" s="35" t="n">
         <v>152351.3871</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>SHB — SHB</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="36" t="n">
         <v>0.0265</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="36" t="n">
         <v>0.0357</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="36" t="n">
         <v>0.0663</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.2078</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="36" t="n">
         <v>0.1717</v>
       </c>
-      <c r="G17" s="39" t="n">
+      <c r="G17" s="40" t="n">
         <v>1.02</v>
       </c>
-      <c r="H17" s="35" t="n">
+      <c r="H17" s="36" t="n">
         <v>0.0201</v>
       </c>
-      <c r="I17" s="34" t="n">
+      <c r="I17" s="35" t="n">
         <v>72941.55738870001</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>OCB — OCB</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="36" t="n">
         <v>0.0359</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="36" t="n">
         <v>0.0475</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="36" t="n">
         <v>0.1067</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="36" t="n">
         <v>0.1118</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="36" t="n">
         <v>0.3709</v>
       </c>
-      <c r="G18" s="39" t="n">
+      <c r="G18" s="40" t="n">
         <v>1.01</v>
       </c>
-      <c r="H18" s="35" t="n">
+      <c r="H18" s="36" t="n">
         <v>0.0272</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I18" s="35" t="n">
         <v>35218.866449</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>BAB — BacABank</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="36" t="n">
         <v>0.0191</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="36" t="n">
         <v>0.0319</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="36" t="n">
         <v>0.0305</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="36" t="n">
         <v>0.0882</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="36" t="n">
         <v>0.5122</v>
       </c>
-      <c r="G19" s="39" t="n">
+      <c r="G19" s="40" t="n">
         <v>0.99</v>
       </c>
-      <c r="H19" s="35" t="n">
+      <c r="H19" s="36" t="n">
         <v>0.0246</v>
       </c>
-      <c r="I19" s="34" t="n">
+      <c r="I19" s="35" t="n">
         <v>13484.8433772</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>NAB — NamABank</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="36" t="n">
         <v>0.0183</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="36" t="n">
         <v>0.0416</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="36" t="n">
         <v>0.05889999999999999</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="36" t="n">
         <v>0.2125</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="36" t="n">
         <v>0.389</v>
       </c>
-      <c r="G20" s="39" t="n">
+      <c r="G20" s="40" t="n">
         <v>1.15</v>
       </c>
-      <c r="H20" s="35" t="n">
+      <c r="H20" s="36" t="n">
         <v>0.0191</v>
       </c>
-      <c r="I20" s="34" t="n">
+      <c r="I20" s="35" t="n">
         <v>28280.5718942</v>
       </c>
     </row>
@@ -15207,7 +15214,7 @@
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Ngày lập: 04/07/2026 08:39</t>
+          <t>Ngày lập: 04/07/2026 11:21</t>
         </is>
       </c>
     </row>
@@ -15266,8 +15273,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="inlineStr">
@@ -15460,13 +15470,18 @@
         <v/>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0304</v>
+        <v>0.0301</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0304</v>
+        <v>0.0301</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0304</v>
+        <v>0.0301</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Năm 1 (2026E) cơ học (YOEA/COF): YOEA=6.88% (gốc 6.98% x hệ số 0.985), COF=5.46% (gốc 5.63% x hệ số 0.97) → NIM cơ học=3.16%. Đã có Q1 thực tế = 2.85% → NIM năm 1 = 50% cơ học + 50% Q1 thực tế = 3.01%. Năm 2/3 GIỮ NGUYÊN bằng năm 1 (không giả định NIM tăng, để định giá an toàn hơn).</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -15628,13 +15643,13 @@
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="n"/>
       <c r="F11" s="14" t="n"/>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="I11" s="16" t="n">
+      <c r="I11" s="17" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -15649,13 +15664,13 @@
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="14" t="n"/>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>0.139043</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="17" t="n">
         <v>0.139043</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="17" t="n">
         <v>0.139043</v>
       </c>
     </row>
@@ -15672,7 +15687,7 @@
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="14" t="n"/>
       <c r="H13" s="14" t="n"/>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="17" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -15687,13 +15702,13 @@
       <c r="D14" s="14" t="n"/>
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="14" t="n"/>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="I14" s="16" t="n">
+      <c r="I14" s="17" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -15708,13 +15723,13 @@
       <c r="D15" s="14" t="n"/>
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>1.67967062575</v>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="18" t="n">
         <v>1.67967062575</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="18" t="n">
         <v>1.67967062575</v>
       </c>
     </row>
@@ -15813,7 +15828,7 @@
           <t>IEA_end gốc (2025A)</t>
         </is>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="19">
         <f>'05_Balance_Sheet'!F2</f>
         <v/>
       </c>
@@ -15824,7 +15839,7 @@
           <t>DepBonds gốc (2025A)</t>
         </is>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <f>SUM('05_Balance_Sheet'!F5:F6)</f>
         <v/>
       </c>
@@ -16027,30 +16042,30 @@
           <t>IEA bình quân (tỷ)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>271213.32</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>286265.358</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>316572.3959999999</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>366530.05</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>440292.5175</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="18">
         <f>(F18+G18)/2</f>
         <v/>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="18">
         <f>(G18+H18)/2</f>
         <v/>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="18">
         <f>(H18+I18)/2</f>
         <v/>
       </c>
@@ -16097,29 +16112,29 @@
           <t>NIM (%)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>0.0367</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>0.0398</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.0393</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.0352</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.0304</v>
       </c>
-      <c r="G4" s="17" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>0.0304</v>
+      <c r="G4" s="18" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>0.0301</v>
       </c>
     </row>
     <row r="5">
@@ -16128,30 +16143,30 @@
           <t>NII (tỷ)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>9946.049000000001</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>11386.597</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>12427.828</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>12906.656</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>13371.161</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>G2*'02_Assumptions'!G6</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>H2*'02_Assumptions'!H6</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>I2*'02_Assumptions'!I6</f>
         <v/>
       </c>
@@ -16162,19 +16177,19 @@
           <t>Thu nhập dịch vụ</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>1542.466</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>2691.98</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>2279.248</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>3363.61</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>4157.757</v>
       </c>
       <c r="G6" s="14" t="n"/>
@@ -16187,19 +16202,19 @@
           <t>Thu nhập ngoại hối</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>373.374</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>410.216</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>779.153</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>318.932</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>693.951</v>
       </c>
       <c r="G7" s="14" t="n"/>
@@ -16212,19 +16227,19 @@
           <t>Thu nhập CK đầu tư</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>1409.742</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>426.255</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>855.841</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>1095.094</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>181.781</v>
       </c>
       <c r="G8" s="14" t="n"/>
@@ -16237,19 +16252,19 @@
           <t>Thu nhập khác</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>245.777</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>702.141</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>-105.313</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>353.935</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>462.131</v>
       </c>
       <c r="G9" s="14" t="n"/>
@@ -16262,28 +16277,28 @@
           <t>Tổng thu nhập ngoài lãi</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>3571.358999999999</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>4230.592000000001</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>3808.929</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>5131.610999999999</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>5623.598999999998</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>6467.138849999998</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>7437.209677499996</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>8478.419032349997</v>
       </c>
     </row>
@@ -16293,30 +16308,30 @@
           <t>Tổng thu nhập HĐ - TOI</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>13517.408</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>15617.189</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>16236.757</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>18038.267</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>18994.76</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="18">
         <f>G5+G10</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="18">
         <f>H5+H10</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="18">
         <f>I5+I10</f>
         <v/>
       </c>
@@ -16327,19 +16342,19 @@
           <t>NII/TOI (%)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>73.58</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>72.91</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>76.54000000000001</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>71.55</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>70.39</v>
       </c>
       <c r="G12" s="14" t="n"/>
@@ -16352,30 +16367,30 @@
           <t>Chi phí HĐ - OPEX</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>4570.696</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>5945.257</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>6701.533</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>6278.857</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>6573.41</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="18">
         <f>G11*'02_Assumptions'!G7</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="18">
         <f>H11*'02_Assumptions'!H7</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="18">
         <f>I11*'02_Assumptions'!I7</f>
         <v/>
       </c>
@@ -16386,30 +16401,30 @@
           <t>PPOP - LN trước dự phòng</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>8946.712</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>9671.932000000001</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>9535.224</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>11759.41</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>12421.35</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="18">
         <f>G11-G13</f>
         <v/>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="18">
         <f>H11-H13</f>
         <v/>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="18">
         <f>I11-I13</f>
         <v/>
       </c>
@@ -16420,19 +16435,19 @@
           <t>PPOP/TOI (%)</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <v>66.19</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>61.93</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>58.73</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>65.19</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="18" t="n">
         <v>65.39</v>
       </c>
       <c r="G15" s="14" t="n"/>
@@ -16445,30 +16460,30 @@
           <t>Dự phòng tín dụng</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <v>2908.49</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1843.644</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>3946.265</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>4159.212</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="18" t="n">
         <v>3190.272</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="18">
         <f>(('05_Balance_Sheet'!F3+'05_Balance_Sheet'!G3)/2)*'02_Assumptions'!G8</f>
         <v/>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="18">
         <f>(('05_Balance_Sheet'!G3+'05_Balance_Sheet'!H3)/2)*'02_Assumptions'!H8</f>
         <v/>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="18">
         <f>(('05_Balance_Sheet'!H3+'05_Balance_Sheet'!I3)/2)*'02_Assumptions'!I8</f>
         <v/>
       </c>
@@ -16479,30 +16494,30 @@
           <t>LN trước thuế - PBT</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>6038.222</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>7828.288</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>5588.959</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>7600.198</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>9231.078</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="18">
         <f>G14-G16</f>
         <v/>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="18">
         <f>H14-H16</f>
         <v/>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="18">
         <f>I14-I16</f>
         <v/>
       </c>
@@ -16513,30 +16528,30 @@
           <t>IEA cuối kỳ (tỷ)</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <v>271213.3</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <v>301317.4</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>331827.4</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>401232.7</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="18" t="n">
         <v>479352.3</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="18">
         <f>F18*(1+G3)</f>
         <v/>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="18">
         <f>G18*(1+H3)</f>
         <v/>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="18">
         <f>H18*(1+I3)</f>
         <v/>
       </c>
@@ -16658,58 +16673,58 @@
           <t>Thu nhập lãi thuần - NII</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>2810.324</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>2831.379</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>3034.868</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>2740.672</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>2779.678</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="18" t="n">
         <v>2736.874</v>
       </c>
-      <c r="H2" s="17" t="n">
+      <c r="H2" s="18" t="n">
         <v>2729.027</v>
       </c>
-      <c r="I2" s="17" t="n">
+      <c r="I2" s="18" t="n">
         <v>2962.701</v>
       </c>
-      <c r="J2" s="17" t="n">
+      <c r="J2" s="18" t="n">
         <v>3996.093</v>
       </c>
-      <c r="K2" s="17" t="n">
+      <c r="K2" s="18" t="n">
         <v>3427.386</v>
       </c>
-      <c r="L2" s="17" t="n">
+      <c r="L2" s="18" t="n">
         <v>3236.772</v>
       </c>
-      <c r="M2" s="17" t="n">
+      <c r="M2" s="18" t="n">
         <v>3173.833</v>
       </c>
-      <c r="N2" s="17" t="n">
+      <c r="N2" s="18" t="n">
         <v>3068.665</v>
       </c>
-      <c r="O2" s="17" t="n">
+      <c r="O2" s="18" t="n">
         <v>3383.618</v>
       </c>
-      <c r="P2" s="17" t="n">
+      <c r="P2" s="18" t="n">
         <v>3151.325</v>
       </c>
-      <c r="Q2" s="17" t="n">
+      <c r="Q2" s="18" t="n">
         <v>3237.619</v>
       </c>
-      <c r="R2" s="17" t="n">
+      <c r="R2" s="18" t="n">
         <v>3598.599</v>
       </c>
-      <c r="S2" s="17" t="n">
+      <c r="S2" s="18" t="n">
         <v>3459.591</v>
       </c>
     </row>
@@ -16719,58 +16734,58 @@
           <t>Thu nhập ngoài lãi</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>800.827</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>784.616</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>1537.967</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>1024.315</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>883.694</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="18" t="n">
         <v>922.192</v>
       </c>
-      <c r="H3" s="17" t="n">
+      <c r="H3" s="18" t="n">
         <v>1188.152</v>
       </c>
-      <c r="I3" s="17" t="n">
+      <c r="I3" s="18" t="n">
         <v>1251.488</v>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="18" t="n">
         <v>447.138</v>
       </c>
-      <c r="K3" s="17" t="n">
+      <c r="K3" s="18" t="n">
         <v>1257.781</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="18" t="n">
         <v>999.386</v>
       </c>
-      <c r="M3" s="17" t="n">
+      <c r="M3" s="18" t="n">
         <v>821.471</v>
       </c>
-      <c r="N3" s="17" t="n">
+      <c r="N3" s="18" t="n">
         <v>2052.973</v>
       </c>
-      <c r="O3" s="17" t="n">
+      <c r="O3" s="18" t="n">
         <v>1098.85</v>
       </c>
-      <c r="P3" s="17" t="n">
+      <c r="P3" s="18" t="n">
         <v>1464.405</v>
       </c>
-      <c r="Q3" s="17" t="n">
+      <c r="Q3" s="18" t="n">
         <v>1287.443</v>
       </c>
-      <c r="R3" s="17" t="n">
+      <c r="R3" s="18" t="n">
         <v>1772.901</v>
       </c>
-      <c r="S3" s="17" t="n">
+      <c r="S3" s="18" t="n">
         <v>1439.744</v>
       </c>
     </row>
@@ -16780,58 +16795,58 @@
           <t>Tổng thu nhập HĐ - TOI</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>3611.151</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>3615.995</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>4572.835</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>3764.987</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>3663.372</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="18" t="n">
         <v>3659.066</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>3917.179</v>
       </c>
-      <c r="I4" s="17" t="n">
+      <c r="I4" s="18" t="n">
         <v>4214.189</v>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="18" t="n">
         <v>4443.231</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="18" t="n">
         <v>4685.167</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="18" t="n">
         <v>4236.158</v>
       </c>
-      <c r="M4" s="17" t="n">
+      <c r="M4" s="18" t="n">
         <v>3995.304</v>
       </c>
-      <c r="N4" s="17" t="n">
+      <c r="N4" s="18" t="n">
         <v>5121.638</v>
       </c>
-      <c r="O4" s="17" t="n">
+      <c r="O4" s="18" t="n">
         <v>4482.468</v>
       </c>
-      <c r="P4" s="17" t="n">
+      <c r="P4" s="18" t="n">
         <v>4615.73</v>
       </c>
-      <c r="Q4" s="17" t="n">
+      <c r="Q4" s="18" t="n">
         <v>4525.062</v>
       </c>
-      <c r="R4" s="17" t="n">
+      <c r="R4" s="18" t="n">
         <v>5371.5</v>
       </c>
-      <c r="S4" s="17" t="n">
+      <c r="S4" s="18" t="n">
         <v>4899.335</v>
       </c>
     </row>
@@ -16841,58 +16856,58 @@
           <t>Chi phí hoạt động - OPEX</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>1406.99</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>1237.583</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>1762.811</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>1298.798</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>1646.065</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>1579.089</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <v>1930.622</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>1345.558</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="18" t="n">
         <v>1843.428</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="K5" s="18" t="n">
         <v>1675.773</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="18" t="n">
         <v>1383.027</v>
       </c>
-      <c r="M5" s="17" t="n">
+      <c r="M5" s="18" t="n">
         <v>1426.37</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="18" t="n">
         <v>1793.687</v>
       </c>
-      <c r="O5" s="17" t="n">
+      <c r="O5" s="18" t="n">
         <v>1883.976</v>
       </c>
-      <c r="P5" s="17" t="n">
+      <c r="P5" s="18" t="n">
         <v>1753.628</v>
       </c>
-      <c r="Q5" s="17" t="n">
+      <c r="Q5" s="18" t="n">
         <v>1713.927</v>
       </c>
-      <c r="R5" s="17" t="n">
+      <c r="R5" s="18" t="n">
         <v>1221.879</v>
       </c>
-      <c r="S5" s="17" t="n">
+      <c r="S5" s="18" t="n">
         <v>2246.554</v>
       </c>
     </row>
@@ -16902,58 +16917,58 @@
           <t>LN trước dự phòng - PPOP</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>2204.161</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>2378.412</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>2810.024</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>2466.189</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>2017.307</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>2079.977</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <v>1986.557</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>2868.631</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="18" t="n">
         <v>2599.803</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="18" t="n">
         <v>3009.394</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="18" t="n">
         <v>2853.131</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="18" t="n">
         <v>2568.934</v>
       </c>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="18" t="n">
         <v>3327.951</v>
       </c>
-      <c r="O6" s="17" t="n">
+      <c r="O6" s="18" t="n">
         <v>2598.492</v>
       </c>
-      <c r="P6" s="17" t="n">
+      <c r="P6" s="18" t="n">
         <v>2862.102</v>
       </c>
-      <c r="Q6" s="17" t="n">
+      <c r="Q6" s="18" t="n">
         <v>2811.135</v>
       </c>
-      <c r="R6" s="17" t="n">
+      <c r="R6" s="18" t="n">
         <v>4149.621</v>
       </c>
-      <c r="S6" s="17" t="n">
+      <c r="S6" s="18" t="n">
         <v>2652.781</v>
       </c>
     </row>
@@ -16963,58 +16978,58 @@
           <t>Dự phòng tín dụng</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>559.5700000000001</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>755.265</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>645.341</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>328.474</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>114.564</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <v>314.976</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <v>368.12</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <v>1292.974</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <v>1970.195</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="18" t="n">
         <v>1180.8</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="18" t="n">
         <v>949.11</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="18" t="n">
         <v>838.348</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="18" t="n">
         <v>1190.954</v>
       </c>
-      <c r="O7" s="17" t="n">
+      <c r="O7" s="18" t="n">
         <v>489.617</v>
       </c>
-      <c r="P7" s="17" t="n">
+      <c r="P7" s="18" t="n">
         <v>824.744</v>
       </c>
-      <c r="Q7" s="17" t="n">
+      <c r="Q7" s="18" t="n">
         <v>909.278</v>
       </c>
-      <c r="R7" s="17" t="n">
+      <c r="R7" s="18" t="n">
         <v>966.633</v>
       </c>
-      <c r="S7" s="17" t="n">
+      <c r="S7" s="18" t="n">
         <v>546.962</v>
       </c>
     </row>
@@ -17024,58 +17039,58 @@
           <t>LN trước thuế - PBT</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>1644.591</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>1623.147</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>2164.683</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>2137.715</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>1902.743</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <v>1765.001</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="18" t="n">
         <v>1618.437</v>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="18" t="n">
         <v>1575.657</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="18" t="n">
         <v>629.6079999999999</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="18" t="n">
         <v>1828.594</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="18" t="n">
         <v>1904.021</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="18" t="n">
         <v>1730.586</v>
       </c>
-      <c r="N8" s="17" t="n">
+      <c r="N8" s="18" t="n">
         <v>2136.997</v>
       </c>
-      <c r="O8" s="17" t="n">
+      <c r="O8" s="18" t="n">
         <v>2108.875</v>
       </c>
-      <c r="P8" s="17" t="n">
+      <c r="P8" s="18" t="n">
         <v>2037.358</v>
       </c>
-      <c r="Q8" s="17" t="n">
+      <c r="Q8" s="18" t="n">
         <v>1901.857</v>
       </c>
-      <c r="R8" s="17" t="n">
+      <c r="R8" s="18" t="n">
         <v>3182.988</v>
       </c>
-      <c r="S8" s="17" t="n">
+      <c r="S8" s="18" t="n">
         <v>2105.819</v>
       </c>
     </row>
@@ -17085,58 +17100,58 @@
           <t>LN sau thuế - NPAT</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>1315.133</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>1299.4</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>1730.465</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>1711.622</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>1519.328</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>1413.242</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>1293.105</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <v>1262.841</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>493.932</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="18" t="n">
         <v>1462.797</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="18" t="n">
         <v>1522.559</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <v>1383.025</v>
       </c>
-      <c r="N9" s="17" t="n">
+      <c r="N9" s="18" t="n">
         <v>1703.253</v>
       </c>
-      <c r="O9" s="17" t="n">
+      <c r="O9" s="18" t="n">
         <v>1686.691</v>
       </c>
-      <c r="P9" s="17" t="n">
+      <c r="P9" s="18" t="n">
         <v>1629.604</v>
       </c>
-      <c r="Q9" s="17" t="n">
+      <c r="Q9" s="18" t="n">
         <v>1520.64</v>
       </c>
-      <c r="R9" s="17" t="n">
+      <c r="R9" s="18" t="n">
         <v>2565.066</v>
       </c>
-      <c r="S9" s="17" t="n">
+      <c r="S9" s="18" t="n">
         <v>1682.225</v>
       </c>
     </row>
@@ -17146,58 +17161,58 @@
           <t>Chi phí lãi (Int Exp)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>489.876</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>511.384</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>680.625</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>683.797</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>816.174</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>695.739</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>803.609</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>665.872</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <v>114.08</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="18" t="n">
         <v>715.126</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="18" t="n">
         <v>945.1799999999999</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>794.465</v>
       </c>
-      <c r="N10" s="17" t="n">
+      <c r="N10" s="18" t="n">
         <v>908.8390000000001</v>
       </c>
-      <c r="O10" s="17" t="n">
+      <c r="O10" s="18" t="n">
         <v>909.938</v>
       </c>
-      <c r="P10" s="17" t="n">
+      <c r="P10" s="18" t="n">
         <v>988.763</v>
       </c>
-      <c r="Q10" s="17" t="n">
+      <c r="Q10" s="18" t="n">
         <v>1034.974</v>
       </c>
-      <c r="R10" s="17" t="n">
+      <c r="R10" s="18" t="n">
         <v>1224.082</v>
       </c>
-      <c r="S10" s="17" t="n">
+      <c r="S10" s="18" t="n">
         <v>1252.429</v>
       </c>
     </row>
@@ -17268,30 +17283,30 @@
           <t>Thu nhập lãi thuần (NII)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>9946.049000000001</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>11386.597</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>12427.828</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>12906.656</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>13371.161</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="18">
         <f>'03_Income_Model'!G5</f>
         <v/>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="18">
         <f>'03_Income_Model'!H5</f>
         <v/>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="18">
         <f>'03_Income_Model'!I5</f>
         <v/>
       </c>
@@ -17302,30 +17317,30 @@
           <t>Tổng thu nhập hoạt động (TOI)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>13517.408</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>15617.189</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>16236.757</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>18038.267</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>18994.76</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="18">
         <f>SUM(G2+'03_Income_Model'!G10)</f>
         <v/>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="18">
         <f>SUM(H2+'03_Income_Model'!H10)</f>
         <v/>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="18">
         <f>SUM(I2+'03_Income_Model'!I10)</f>
         <v/>
       </c>
@@ -17336,30 +17351,30 @@
           <t>Lợi nhuận trước dự phòng (PPOP)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>8946.712</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>9671.932000000001</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>9535.224</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>11759.41</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>12421.35</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="18">
         <f>'03_Income_Model'!G14</f>
         <v/>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="18">
         <f>'03_Income_Model'!H14</f>
         <v/>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="18">
         <f>'03_Income_Model'!I14</f>
         <v/>
       </c>
@@ -17370,30 +17385,30 @@
           <t>LNST (NPAT)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>4829.179</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>6260.744</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>4463.325</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>6071.634</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>7402.001</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>('03_Income_Model'!G17)-MAX(('03_Income_Model'!G17)*'02_Assumptions'!G14,0)</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>('03_Income_Model'!H17)-MAX(('03_Income_Model'!H17)*'02_Assumptions'!H14,0)</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>('03_Income_Model'!I17)-MAX(('03_Income_Model'!I17)*'02_Assumptions'!I14,0)</f>
         <v/>
       </c>
@@ -17549,58 +17564,58 @@
           <t>Tổng tài sản</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>292827.078</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>302622.532</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>310769.29</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>317327.732</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>328634.007</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="18" t="n">
         <v>343522.216</v>
       </c>
-      <c r="H2" s="17" t="n">
+      <c r="H2" s="18" t="n">
         <v>343406.813</v>
       </c>
-      <c r="I2" s="17" t="n">
+      <c r="I2" s="18" t="n">
         <v>344402.552</v>
       </c>
-      <c r="J2" s="17" t="n">
+      <c r="J2" s="18" t="n">
         <v>356636.84</v>
       </c>
-      <c r="K2" s="17" t="n">
+      <c r="K2" s="18" t="n">
         <v>355870.488</v>
       </c>
-      <c r="L2" s="17" t="n">
+      <c r="L2" s="18" t="n">
         <v>361554.998</v>
       </c>
-      <c r="M2" s="17" t="n">
+      <c r="M2" s="18" t="n">
         <v>385352.239</v>
       </c>
-      <c r="N2" s="17" t="n">
+      <c r="N2" s="18" t="n">
         <v>418028.391</v>
       </c>
-      <c r="O2" s="17" t="n">
+      <c r="O2" s="18" t="n">
         <v>388891.15</v>
       </c>
-      <c r="P2" s="17" t="n">
+      <c r="P2" s="18" t="n">
         <v>428589.979</v>
       </c>
-      <c r="Q2" s="17" t="n">
+      <c r="Q2" s="18" t="n">
         <v>451893.195</v>
       </c>
-      <c r="R2" s="17" t="n">
+      <c r="R2" s="18" t="n">
         <v>505901.57</v>
       </c>
-      <c r="S2" s="17" t="n">
+      <c r="S2" s="18" t="n">
         <v>527169.377</v>
       </c>
     </row>
@@ -17610,58 +17625,58 @@
           <t>Tiền mặt &amp; NHNN</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>20593.157</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>16553.609</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>16425.331</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>11580.412</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>14415.433</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="18" t="n">
         <v>12403.834</v>
       </c>
-      <c r="H3" s="17" t="n">
+      <c r="H3" s="18" t="n">
         <v>11395.331</v>
       </c>
-      <c r="I3" s="17" t="n">
+      <c r="I3" s="18" t="n">
         <v>12499.903</v>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="18" t="n">
         <v>11550.529</v>
       </c>
-      <c r="K3" s="17" t="n">
+      <c r="K3" s="18" t="n">
         <v>13167.518</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="18" t="n">
         <v>10383.864</v>
       </c>
-      <c r="M3" s="17" t="n">
+      <c r="M3" s="18" t="n">
         <v>14907.331</v>
       </c>
-      <c r="N3" s="17" t="n">
+      <c r="N3" s="18" t="n">
         <v>24001.104</v>
       </c>
-      <c r="O3" s="17" t="n">
+      <c r="O3" s="18" t="n">
         <v>18330.187</v>
       </c>
-      <c r="P3" s="17" t="n">
+      <c r="P3" s="18" t="n">
         <v>11552.156</v>
       </c>
-      <c r="Q3" s="17" t="n">
+      <c r="Q3" s="18" t="n">
         <v>22219.104</v>
       </c>
-      <c r="R3" s="17" t="n">
+      <c r="R3" s="18" t="n">
         <v>22164.361</v>
       </c>
-      <c r="S3" s="17" t="n">
+      <c r="S3" s="18" t="n">
         <v>12660.977</v>
       </c>
     </row>
@@ -17671,58 +17686,58 @@
           <t>TG các TCTD khác</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>48752.914</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>37628.452</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>40738.575</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>46897.369</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>53364.944</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="18" t="n">
         <v>56285.508</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>56630.247</v>
       </c>
-      <c r="I4" s="17" t="n">
+      <c r="I4" s="18" t="n">
         <v>58926.396</v>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="18" t="n">
         <v>52351.827</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="18" t="n">
         <v>56447.319</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="18" t="n">
         <v>55159.384</v>
       </c>
-      <c r="M4" s="17" t="n">
+      <c r="M4" s="18" t="n">
         <v>54515.768</v>
       </c>
-      <c r="N4" s="17" t="n">
+      <c r="N4" s="18" t="n">
         <v>70520.7</v>
       </c>
-      <c r="O4" s="17" t="n">
+      <c r="O4" s="18" t="n">
         <v>35189.69</v>
       </c>
-      <c r="P4" s="17" t="n">
+      <c r="P4" s="18" t="n">
         <v>59990.1</v>
       </c>
-      <c r="Q4" s="17" t="n">
+      <c r="Q4" s="18" t="n">
         <v>65344.16</v>
       </c>
-      <c r="R4" s="17" t="n">
+      <c r="R4" s="18" t="n">
         <v>103388.411</v>
       </c>
-      <c r="S4" s="17" t="n">
+      <c r="S4" s="18" t="n">
         <v>109316.911</v>
       </c>
     </row>
@@ -17732,58 +17747,58 @@
           <t>Cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>139462.565</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>147720.192</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>149008.131</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>154164.205</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>159160.375</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>170658.669</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <v>174730.627</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>177431.789</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="18" t="n">
         <v>202586.102</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="K5" s="18" t="n">
         <v>198127.997</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="18" t="n">
         <v>210529.898</v>
       </c>
-      <c r="M5" s="17" t="n">
+      <c r="M5" s="18" t="n">
         <v>231562.431</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="18" t="n">
         <v>247238.856</v>
       </c>
-      <c r="O5" s="17" t="n">
+      <c r="O5" s="18" t="n">
         <v>259070.461</v>
       </c>
-      <c r="P5" s="17" t="n">
+      <c r="P5" s="18" t="n">
         <v>281188.723</v>
       </c>
-      <c r="Q5" s="17" t="n">
+      <c r="Q5" s="18" t="n">
         <v>292020.111</v>
       </c>
-      <c r="R5" s="17" t="n">
+      <c r="R5" s="18" t="n">
         <v>302186.389</v>
       </c>
-      <c r="S5" s="17" t="n">
+      <c r="S5" s="18" t="n">
         <v>312044.784</v>
       </c>
     </row>
@@ -17793,58 +17808,58 @@
           <t>CK đầu tư</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>62404.684</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>77405.03</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>76531.823</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>76108.912</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>74376.644</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>78679.929</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <v>73758.379</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>67866.961</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="18" t="n">
         <v>65335.805</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="18" t="n">
         <v>62151.6</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="18" t="n">
         <v>60864.989</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="18" t="n">
         <v>63892.59</v>
       </c>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="18" t="n">
         <v>59472.044</v>
       </c>
-      <c r="O6" s="17" t="n">
+      <c r="O6" s="18" t="n">
         <v>59909.064</v>
       </c>
-      <c r="P6" s="17" t="n">
+      <c r="P6" s="18" t="n">
         <v>60147.095</v>
       </c>
-      <c r="Q6" s="17" t="n">
+      <c r="Q6" s="18" t="n">
         <v>57166.207</v>
       </c>
-      <c r="R6" s="17" t="n">
+      <c r="R6" s="18" t="n">
         <v>51613.17</v>
       </c>
-      <c r="S6" s="17" t="n">
+      <c r="S6" s="18" t="n">
         <v>57531.215</v>
       </c>
     </row>
@@ -17854,58 +17869,58 @@
           <t>Tiền gửi khách hàng</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>139562.262</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>152538.738</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>156336.66</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>162694.692</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>194959.921</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <v>200998.074</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <v>199126.911</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <v>193753.424</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <v>208261.56</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="18" t="n">
         <v>190827.358</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="18" t="n">
         <v>202997.118</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="18" t="n">
         <v>224821.01</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="18" t="n">
         <v>242805.789</v>
       </c>
-      <c r="O7" s="17" t="n">
+      <c r="O7" s="18" t="n">
         <v>233114.646</v>
       </c>
-      <c r="P7" s="17" t="n">
+      <c r="P7" s="18" t="n">
         <v>246844.312</v>
       </c>
-      <c r="Q7" s="17" t="n">
+      <c r="Q7" s="18" t="n">
         <v>260245.786</v>
       </c>
-      <c r="R7" s="17" t="n">
+      <c r="R7" s="18" t="n">
         <v>279050.251</v>
       </c>
-      <c r="S7" s="17" t="n">
+      <c r="S7" s="18" t="n">
         <v>267038.156</v>
       </c>
     </row>
@@ -17915,58 +17930,58 @@
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>25987.981</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>27380.476</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>29008.102</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>30637.298</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>32239.052</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <v>33662.293</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="18" t="n">
         <v>30985.939</v>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="18" t="n">
         <v>32383.937</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="18" t="n">
         <v>32742.712</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="18" t="n">
         <v>34190.213</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="18" t="n">
         <v>35609.007</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="18" t="n">
         <v>36311.082</v>
       </c>
-      <c r="N8" s="17" t="n">
+      <c r="N8" s="18" t="n">
         <v>37594.469</v>
       </c>
-      <c r="O8" s="17" t="n">
+      <c r="O8" s="18" t="n">
         <v>39491.596</v>
       </c>
-      <c r="P8" s="17" t="n">
+      <c r="P8" s="18" t="n">
         <v>38229.908</v>
       </c>
-      <c r="Q8" s="17" t="n">
+      <c r="Q8" s="18" t="n">
         <v>39993.24</v>
       </c>
-      <c r="R8" s="17" t="n">
+      <c r="R8" s="18" t="n">
         <v>46048.761</v>
       </c>
-      <c r="S8" s="17" t="n">
+      <c r="S8" s="18" t="n">
         <v>48034.318</v>
       </c>
     </row>
@@ -17976,58 +17991,58 @@
           <t>TPDN (trái phiếu TCKT)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>18576.663</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>27589.255</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>23273.644</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>22346.342</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>21623.651</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>20472.383</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>17902.544</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <v>15867.333</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>12156.199</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="18" t="n">
         <v>9305.299000000001</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="18" t="n">
         <v>12349.357</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <v>12096.16</v>
       </c>
-      <c r="N9" s="17" t="n">
+      <c r="N9" s="18" t="n">
         <v>10309.787</v>
       </c>
-      <c r="O9" s="17" t="n">
+      <c r="O9" s="18" t="n">
         <v>8309.571</v>
       </c>
-      <c r="P9" s="17" t="n">
+      <c r="P9" s="18" t="n">
         <v>7945.028</v>
       </c>
-      <c r="Q9" s="17" t="n">
+      <c r="Q9" s="18" t="n">
         <v>6660.755</v>
       </c>
-      <c r="R9" s="17" t="n">
+      <c r="R9" s="18" t="n">
         <v>4648.74</v>
       </c>
-      <c r="S9" s="17" t="n">
+      <c r="S9" s="18" t="n">
         <v>2707.522</v>
       </c>
     </row>
@@ -18037,58 +18052,58 @@
           <t>Giấy tờ có giá (Bonds)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>35405.147</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>37220.237</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>31267.793</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>29842.92</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>20429.954</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>19085.909</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>15266.125</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>12168.977</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <v>24216.267</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="18" t="n">
         <v>31811.364</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="18" t="n">
         <v>36013.262</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>36284.473</v>
       </c>
-      <c r="N10" s="17" t="n">
+      <c r="N10" s="18" t="n">
         <v>36632.2</v>
       </c>
-      <c r="O10" s="17" t="n">
+      <c r="O10" s="18" t="n">
         <v>38602.2</v>
       </c>
-      <c r="P10" s="17" t="n">
+      <c r="P10" s="18" t="n">
         <v>43958.6</v>
       </c>
-      <c r="Q10" s="17" t="n">
+      <c r="Q10" s="18" t="n">
         <v>44305.8</v>
       </c>
-      <c r="R10" s="17" t="n">
+      <c r="R10" s="18" t="n">
         <v>58825</v>
       </c>
-      <c r="S10" s="17" t="n">
+      <c r="S10" s="18" t="n">
         <v>59646.208</v>
       </c>
     </row>
@@ -18098,58 +18113,58 @@
           <t>Tiền gửi Kho bạc NN</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>20428.826</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>22752.536</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>27399.078</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>27538.168</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>26160.807</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>24375.139</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <v>28346.835</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="I11" s="18" t="n">
         <v>26794.751</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="18" t="n">
         <v>24000.029</v>
       </c>
-      <c r="K11" s="17" t="n">
+      <c r="K11" s="18" t="n">
         <v>24509.224</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="18" t="n">
         <v>24485.464</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="18" t="n">
         <v>19769.01</v>
       </c>
-      <c r="N11" s="17" t="n">
+      <c r="N11" s="18" t="n">
         <v>15045.341</v>
       </c>
-      <c r="O11" s="17" t="n">
+      <c r="O11" s="18" t="n">
         <v>19810.039</v>
       </c>
-      <c r="P11" s="17" t="n">
+      <c r="P11" s="18" t="n">
         <v>19884.222</v>
       </c>
-      <c r="Q11" s="17" t="n">
+      <c r="Q11" s="18" t="n">
         <v>13354.784</v>
       </c>
-      <c r="R11" s="17" t="n">
+      <c r="R11" s="18" t="n">
         <v>23428.071</v>
       </c>
-      <c r="S11" s="17" t="n">
+      <c r="S11" s="18" t="n">
         <v>39801.498</v>
       </c>
     </row>
@@ -18159,58 +18174,58 @@
           <t>Tiền gửi ký quỹ (trừ đi)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>7098.093</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>6224.787</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>6519.178</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>6820.814</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>6277.778</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>6214.928</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="18" t="n">
         <v>6265.598</v>
       </c>
-      <c r="I12" s="17" t="n">
+      <c r="I12" s="18" t="n">
         <v>6790.146</v>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="18" t="n">
         <v>10631.97</v>
       </c>
-      <c r="K12" s="17" t="n">
+      <c r="K12" s="18" t="n">
         <v>10940.312</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L12" s="18" t="n">
         <v>9873.918</v>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="18" t="n">
         <v>10137.933</v>
       </c>
-      <c r="N12" s="17" t="n">
+      <c r="N12" s="18" t="n">
         <v>10094.184</v>
       </c>
-      <c r="O12" s="17" t="n">
+      <c r="O12" s="18" t="n">
         <v>9174.156000000001</v>
       </c>
-      <c r="P12" s="17" t="n">
+      <c r="P12" s="18" t="n">
         <v>9965.962</v>
       </c>
-      <c r="Q12" s="17" t="n">
+      <c r="Q12" s="18" t="n">
         <v>10086.044</v>
       </c>
-      <c r="R12" s="17" t="n">
+      <c r="R12" s="18" t="n">
         <v>11373.185</v>
       </c>
-      <c r="S12" s="17" t="n">
+      <c r="S12" s="18" t="n">
         <v>9368.697</v>
       </c>
     </row>
@@ -18220,58 +18235,58 @@
           <t>Vốn chuyên dùng (trừ đi)</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>401.664</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>409.19</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>412.906</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>419.769</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>164.923</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>153.474</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <v>101.049</v>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="18" t="n">
         <v>82.468</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="18" t="n">
         <v>74.31100000000001</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="K13" s="18" t="n">
         <v>75.569</v>
       </c>
-      <c r="L13" s="17" t="n">
+      <c r="L13" s="18" t="n">
         <v>81.65900000000001</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="18" t="n">
         <v>86.548</v>
       </c>
-      <c r="N13" s="17" t="n">
+      <c r="N13" s="18" t="n">
         <v>93.60599999999999</v>
       </c>
-      <c r="O13" s="17" t="n">
+      <c r="O13" s="18" t="n">
         <v>103.644</v>
       </c>
-      <c r="P13" s="17" t="n">
+      <c r="P13" s="18" t="n">
         <v>118.537</v>
       </c>
-      <c r="Q13" s="17" t="n">
+      <c r="Q13" s="18" t="n">
         <v>126.59</v>
       </c>
-      <c r="R13" s="17" t="n">
+      <c r="R13" s="18" t="n">
         <v>140.504</v>
       </c>
-      <c r="S13" s="17" t="n">
+      <c r="S13" s="18" t="n">
         <v>150.825</v>
       </c>
     </row>
@@ -18281,58 +18296,58 @@
           <t>Tài sản sinh lãi (IEA)</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>271213.32</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>279307.2830000001</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>282703.86</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>288750.898</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>301317.396</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>318027.94</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="18" t="n">
         <v>316514.584</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="18" t="n">
         <v>316725.049</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="18" t="n">
         <v>331824.263</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="K14" s="18" t="n">
         <v>329894.434</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="18" t="n">
         <v>336938.135</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="18" t="n">
         <v>364878.12</v>
       </c>
-      <c r="N14" s="17" t="n">
+      <c r="N14" s="18" t="n">
         <v>401232.704</v>
       </c>
-      <c r="O14" s="17" t="n">
+      <c r="O14" s="18" t="n">
         <v>372499.402</v>
       </c>
-      <c r="P14" s="17" t="n">
+      <c r="P14" s="18" t="n">
         <v>412878.074</v>
       </c>
-      <c r="Q14" s="17" t="n">
+      <c r="Q14" s="18" t="n">
         <v>436749.582</v>
       </c>
-      <c r="R14" s="17" t="n">
+      <c r="R14" s="18" t="n">
         <v>479352.331</v>
       </c>
-      <c r="S14" s="17" t="n">
+      <c r="S14" s="18" t="n">
         <v>491553.887</v>
       </c>
     </row>
@@ -18342,75 +18357,75 @@
           <t>Tổng tín dụng (tỷ)</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="18">
         <f>B5+B9</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="18">
         <f>C5+C9</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <f>D5+D9</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="18">
         <f>E5+E9</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="18">
         <f>F5+F9</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="18">
         <f>G5+G9</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="18">
         <f>H5+H9</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="18">
         <f>I5+I9</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="18">
         <f>J5+J9</f>
         <v/>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="18">
         <f>K5+K9</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="18">
         <f>L5+L9</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="18">
         <f>M5+M9</f>
         <v/>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="18">
         <f>N5+N9</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="18">
         <f>O5+O9</f>
         <v/>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="18">
         <f>P5+P9</f>
         <v/>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="18">
         <f>Q5+Q9</f>
         <v/>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="18">
         <f>R5+R9</f>
         <v/>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="18">
         <f>S5+S9</f>
         <v/>
       </c>
@@ -18421,75 +18436,75 @@
           <t>Tổng huy động (tỷ)</t>
         </is>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="18">
         <f>B7+B10+B17+B11*0.0-B12-B13</f>
         <v/>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="18">
         <f>C7+C10+C17+C11*0.0-C12-C13</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="18">
         <f>D7+D10+D17+D11*0.0-D12-D13</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="18">
         <f>E7+E10+E17+E11*0.0-E12-E13</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="18">
         <f>F7+F10+F17+F11*0.0-F12-F13</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="18">
         <f>G7+G10+G17+G11*0.5-G12-G13</f>
         <v/>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="18">
         <f>H7+H10+H17+H11*0.5-H12-H13</f>
         <v/>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="18">
         <f>I7+I10+I17+I11*0.5-I12-I13</f>
         <v/>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="18">
         <f>J7+J10+J17+J11*0.5-J12-J13</f>
         <v/>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="18">
         <f>K7+K10+K17+K11*0.4-K12-K13</f>
         <v/>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="18">
         <f>L7+L10+L17+L11*0.4-L12-L13</f>
         <v/>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="18">
         <f>M7+M10+M17+M11*0.4-M12-M13</f>
         <v/>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="18">
         <f>N7+N10+N17+N11*0.4-N12-N13</f>
         <v/>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="18">
         <f>O7+O10+O17+O11*0.2-O12-O13</f>
         <v/>
       </c>
-      <c r="P16" s="17">
+      <c r="P16" s="18">
         <f>P7+P10+P17+P11*0.2-P12-P13</f>
         <v/>
       </c>
-      <c r="Q16" s="17">
+      <c r="Q16" s="18">
         <f>Q7+Q10+Q17+Q11*0.2-Q12-Q13</f>
         <v/>
       </c>
-      <c r="R16" s="17">
+      <c r="R16" s="18">
         <f>R7+R10+R17+R11*0.2-R12-R13</f>
         <v/>
       </c>
-      <c r="S16" s="17">
+      <c r="S16" s="18">
         <f>S7+S10+S17+S11*0.2-S12-S13</f>
         <v/>
       </c>
@@ -18500,58 +18515,58 @@
           <t>Tiền gửi của TCTD khác</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>53315.464</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>45449.755</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>44097.489</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>50077.494</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>47265.806</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>59511.279</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <v>59164.724</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="18" t="n">
         <v>79329.698</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="18" t="n">
         <v>62399.297</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="18" t="n">
         <v>66911.90300000001</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="18" t="n">
         <v>59481.873</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="18" t="n">
         <v>70603.246</v>
       </c>
-      <c r="N17" s="17" t="n">
+      <c r="N17" s="18" t="n">
         <v>76597.834</v>
       </c>
-      <c r="O17" s="17" t="n">
+      <c r="O17" s="18" t="n">
         <v>43029.794</v>
       </c>
-      <c r="P17" s="17" t="n">
+      <c r="P17" s="18" t="n">
         <v>55969.792</v>
       </c>
-      <c r="Q17" s="17" t="n">
+      <c r="Q17" s="18" t="n">
         <v>73030.85799999999</v>
       </c>
-      <c r="R17" s="17" t="n">
+      <c r="R17" s="18" t="n">
         <v>74215.8</v>
       </c>
-      <c r="S17" s="17" t="n">
+      <c r="S17" s="18" t="n">
         <v>103612.548</v>
       </c>
     </row>
@@ -18622,19 +18637,19 @@
           <t>Tổng tài sản</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>292827.078</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>328634.007</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>356633.972</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>418028.391</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>505901.57</v>
       </c>
       <c r="G2" s="14">
@@ -18656,30 +18671,30 @@
           <t>Cho vay khách hàng (Gross)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>139462.565</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>159160.375</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>202586.102</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>247238.856</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>302186.389</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="18">
         <f>F3*(1+'02_Assumptions'!G4)</f>
         <v/>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="18">
         <f>G3*(1+'02_Assumptions'!H4)</f>
         <v/>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="18">
         <f>H3*(1+'02_Assumptions'!I4)</f>
         <v/>
       </c>
@@ -18690,19 +18705,19 @@
           <t>Trái phiếu doanh nghiệp</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>18576.663</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>21623.651</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>12156.199</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>10309.787</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>4648.74</v>
       </c>
       <c r="G4" s="14">
@@ -18724,30 +18739,30 @@
           <t>Tiền gửi khách hàng</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>139562.262</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>194959.921</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>208261.56</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>242805.789</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>279050.251</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>F5*(1+'02_Assumptions'!G5)</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>G5*(1+'02_Assumptions'!H5)</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>H5*(1+'02_Assumptions'!I5)</f>
         <v/>
       </c>
@@ -18758,19 +18773,19 @@
           <t>Giấy tờ có giá phát hành (Bonds)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>35405.147</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>20429.954</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>24216.267</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>36632.2</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>58825</v>
       </c>
       <c r="G6" s="14">
@@ -18792,19 +18807,19 @@
           <t>Tiền gửi Kho bạc Nhà nước</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>20428.826</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>26160.807</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>23994.029</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>15045.341</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>23428.071</v>
       </c>
       <c r="G7" s="14">
@@ -18826,19 +18841,19 @@
           <t>Tiền gửi ký quỹ (trừ đi)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>7098.093</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>6277.778</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>7436.659</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>10094.184</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>11373.185</v>
       </c>
       <c r="G8" s="14">
@@ -18860,19 +18875,19 @@
           <t>Vốn chuyên dùng (trừ đi)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>401.664</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>164.923</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>74.31100000000001</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>93.60599999999999</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>140.504</v>
       </c>
       <c r="G9" s="14">
@@ -18894,19 +18909,19 @@
           <t>Vốn chủ sở hữu (VCSH)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>25987.07</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>32239.052</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>32742.917</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>37594.469</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>46048.761</v>
       </c>
       <c r="G10" s="14">
@@ -18928,35 +18943,35 @@
           <t>Tổng tín dụng (tỷ)</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="18">
         <f>B3+B4</f>
         <v/>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <f>C3+C4</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>D3+D4</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="18">
         <f>E3+E4</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="18">
         <f>F3+F4</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="18">
         <f>G3+G4</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="18">
         <f>H3+H4</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="18">
         <f>I3+I4</f>
         <v/>
       </c>
@@ -18967,35 +18982,35 @@
           <t>Tổng huy động (tỷ)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="18">
         <f>B5+B6+B13+B7*0.0-B8-B9</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <f>C5+C6+C13+C7*0.0-C8-C9</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>D5+D6+D13+D7*0.5-D8-D9</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="18">
         <f>E5+E6+E13+E7*0.4-E8-E9</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>F5+F6+F13+F7*0.2-F8-F9</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="18">
         <f>G5+G6+G13+G7*0.2-G8-G9</f>
         <v/>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="18">
         <f>H5+H6+H13+H7*0.2-H8-H9</f>
         <v/>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="18">
         <f>I5+I6+I13+I7*0.2-I8-I9</f>
         <v/>
       </c>
@@ -19006,30 +19021,30 @@
           <t>Tiền gửi của TCTD khác</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>53315.464</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>47265.806</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>62399.297</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>76597.834</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>74215.8</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="18">
         <f>F13*(1+'02_Assumptions'!G5)</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="18">
         <f>G13*(1+'02_Assumptions'!H5)</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="18">
         <f>H13*(1+'02_Assumptions'!I5)</f>
         <v/>
       </c>

--- a/Bao cao/TPB/TPB_Model_2026_07_04.xlsx
+++ b/Bao cao/TPB/TPB_Model_2026_07_04.xlsx
@@ -15214,7 +15214,7 @@
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Ngày lập: 04/07/2026 11:21</t>
+          <t>Ngày lập: 04/07/2026 12:01</t>
         </is>
       </c>
     </row>
